--- a/Secuencias_Base_APP_AKC.xlsx
+++ b/Secuencias_Base_APP_AKC.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FFC65FC08FB1EDE630160BFD3BFC529B5A9C7433" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_FFC65FC08FB1EDE630160BFD3BFC529B5A9C7433" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231622A7-B646-6B41-B919-A1DBF73E6870}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="128">
   <si>
     <t>Aparato</t>
   </si>
@@ -90,18 +90,12 @@
     <t>Circulo</t>
   </si>
   <si>
-    <t>Salida finlandesa</t>
-  </si>
-  <si>
     <t>Con arzones:</t>
   </si>
   <si>
     <t>Tijera falsa, tijera</t>
   </si>
   <si>
-    <t>5 circulos sobre arzones</t>
-  </si>
-  <si>
     <t>Bajada lateral</t>
   </si>
   <si>
@@ -132,9 +126,6 @@
     <t>2 circulo en grupa</t>
   </si>
   <si>
-    <t>Splindle a intento de kolivanov</t>
-  </si>
-  <si>
     <t>Cheka circulo Stockly</t>
   </si>
   <si>
@@ -153,9 +144,6 @@
     <t>Sandwich</t>
   </si>
   <si>
-    <t>Plancha dorsal</t>
-  </si>
-  <si>
     <t>3 balanceos</t>
   </si>
   <si>
@@ -165,18 +153,9 @@
     <t>Parado de hombros 5"</t>
   </si>
   <si>
-    <t>Inlocada</t>
-  </si>
-  <si>
-    <t>Dislocada</t>
-  </si>
-  <si>
     <t>Salida de mortal extendido atras</t>
   </si>
   <si>
-    <t>Sandwich a plancha</t>
-  </si>
-  <si>
     <t>3 balances a mas de horizontal</t>
   </si>
   <si>
@@ -213,12 +192,6 @@
     <t>Rodada atrás a sandwich disloque</t>
   </si>
   <si>
-    <t>1 gigante</t>
-  </si>
-  <si>
-    <t>1 molino</t>
-  </si>
-  <si>
     <t>Alemana L sit 5"</t>
   </si>
   <si>
@@ -237,9 +210,6 @@
     <t>Subida de pecho</t>
   </si>
   <si>
-    <t>Balleston</t>
-  </si>
-  <si>
     <t>Cualquier Salida A</t>
   </si>
   <si>
@@ -273,9 +243,6 @@
     <t>Algun corte braq o Yamawaki</t>
   </si>
   <si>
-    <t>3 katos 3" seguidos</t>
-  </si>
-  <si>
     <t>Stemme</t>
   </si>
   <si>
@@ -324,18 +291,12 @@
     <t xml:space="preserve">Cambio directo a </t>
   </si>
   <si>
-    <t>Cambio sencillo salvada</t>
-  </si>
-  <si>
     <t>2 Gigantes CAMBIO SALTADO</t>
   </si>
   <si>
     <t>Intento stalder cerrado</t>
   </si>
   <si>
-    <t>Cambio sencillo 2 molinos</t>
-  </si>
-  <si>
     <t>Adler con 1/2</t>
   </si>
   <si>
@@ -363,9 +324,6 @@
     <t>Hercules o Kip 5"</t>
   </si>
   <si>
-    <t>Plancha Ext, abi o bola 5"</t>
-  </si>
-  <si>
     <t>Kip o Hercules 5"</t>
   </si>
   <si>
@@ -384,9 +342,6 @@
     <t>Kip Cristo 5"</t>
   </si>
   <si>
-    <t>Kip cristo 5"</t>
-  </si>
-  <si>
     <t>Kip plancha 5"</t>
   </si>
   <si>
@@ -394,6 +349,66 @@
   </si>
   <si>
     <t>Kip L 5"</t>
+  </si>
+  <si>
+    <t>2 Rusas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gigante sostenido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gigante pasajero </t>
+  </si>
+  <si>
+    <t>Molino sostenido</t>
+  </si>
+  <si>
+    <t>Molino pasajero</t>
+  </si>
+  <si>
+    <t>2 Stutkhere</t>
+  </si>
+  <si>
+    <t>2 Diamidov</t>
+  </si>
+  <si>
+    <t>Cambio directo 2 molinos</t>
+  </si>
+  <si>
+    <t>Salida finlandesa o de rusas</t>
+  </si>
+  <si>
+    <t>3 circulos sobre arzones</t>
+  </si>
+  <si>
+    <t>Salida finlandesa o rusas</t>
+  </si>
+  <si>
+    <t>1/2 Splindle a intento de kolivanov</t>
+  </si>
+  <si>
+    <t>Semidislocada (rompimiento)</t>
+  </si>
+  <si>
+    <t>2 Dislocadas por encima de anillos</t>
+  </si>
+  <si>
+    <t>Sandwich a semidislocada (rompimiento)</t>
+  </si>
+  <si>
+    <t>Descenso a escuadra abierta (endo)</t>
+  </si>
+  <si>
+    <t>Escuadra abierta (endo)</t>
+  </si>
+  <si>
+    <t>Plancha Ext o pajaro 5"</t>
+  </si>
+  <si>
+    <t>Balleston a cualquier intento de corte braquial</t>
+  </si>
+  <si>
+    <t>Salvada o Stalder</t>
   </si>
 </sst>
 </file>
@@ -761,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.2578125" bestFit="1" customWidth="1"/>
@@ -891,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -905,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -919,7 +934,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -933,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -947,7 +962,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -961,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -975,7 +990,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -989,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1003,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1017,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1031,7 +1046,7 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1045,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1059,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1073,7 +1088,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1087,7 +1102,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1101,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1143,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1157,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1171,7 +1186,7 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -1185,7 +1200,7 @@
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1199,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1213,7 +1228,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1227,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -1241,7 +1256,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -1255,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1269,7 +1284,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -1283,21 +1298,21 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -1308,10 +1323,10 @@
         <v>9</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -1322,10 +1337,10 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -1336,10 +1351,10 @@
         <v>9</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -1350,10 +1365,10 @@
         <v>9</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1364,10 +1379,10 @@
         <v>9</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1378,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -1392,10 +1407,10 @@
         <v>9</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1403,13 +1418,13 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1420,10 +1435,10 @@
         <v>10</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -1434,10 +1449,10 @@
         <v>10</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -1448,7 +1463,7 @@
         <v>10</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" t="s">
         <v>43</v>
@@ -1462,10 +1477,10 @@
         <v>10</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -1476,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="s">
         <v>44</v>
@@ -1490,10 +1505,10 @@
         <v>10</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -1504,10 +1519,10 @@
         <v>10</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -1515,13 +1530,13 @@
         <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -1532,10 +1547,10 @@
         <v>11</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -1546,10 +1561,10 @@
         <v>11</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -1560,10 +1575,10 @@
         <v>11</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -1574,10 +1589,10 @@
         <v>11</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -1588,10 +1603,10 @@
         <v>11</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -1602,10 +1617,10 @@
         <v>11</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -1616,10 +1631,10 @@
         <v>11</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -1630,10 +1645,10 @@
         <v>11</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1641,13 +1656,13 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -1658,10 +1673,10 @@
         <v>12</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -1672,10 +1687,10 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -1686,10 +1701,10 @@
         <v>12</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -1700,10 +1715,10 @@
         <v>12</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -1714,10 +1729,10 @@
         <v>12</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -1728,10 +1743,10 @@
         <v>12</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -1742,10 +1757,10 @@
         <v>12</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -1756,10 +1771,10 @@
         <v>12</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -1770,52 +1785,52 @@
         <v>12</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -1826,10 +1841,10 @@
         <v>9</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -1840,10 +1855,10 @@
         <v>9</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -1854,10 +1869,10 @@
         <v>9</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -1868,10 +1883,10 @@
         <v>9</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -1882,10 +1897,10 @@
         <v>9</v>
       </c>
       <c r="C80">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D80" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -1893,13 +1908,13 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -1907,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -1921,13 +1936,13 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -1938,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -1952,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -1966,10 +1981,10 @@
         <v>10</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -1980,10 +1995,10 @@
         <v>10</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -1994,10 +2009,10 @@
         <v>10</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -2005,13 +2020,13 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -2019,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -2033,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -2047,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -2064,10 +2079,10 @@
         <v>11</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
@@ -2078,10 +2093,10 @@
         <v>11</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
@@ -2092,10 +2107,10 @@
         <v>11</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
@@ -2106,10 +2121,10 @@
         <v>11</v>
       </c>
       <c r="C96">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -2117,13 +2132,13 @@
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -2131,13 +2146,13 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -2145,13 +2160,13 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -2159,13 +2174,13 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -2176,10 +2191,10 @@
         <v>12</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -2190,10 +2205,10 @@
         <v>12</v>
       </c>
       <c r="C102">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -2204,10 +2219,10 @@
         <v>12</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -2218,66 +2233,66 @@
         <v>12</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D105" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D107" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -2288,10 +2303,10 @@
         <v>9</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -2302,10 +2317,10 @@
         <v>9</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -2316,10 +2331,10 @@
         <v>9</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -2330,10 +2345,10 @@
         <v>9</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -2341,13 +2356,13 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -2355,13 +2370,13 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -2369,13 +2384,13 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D115" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -2383,13 +2398,13 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -2400,10 +2415,10 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -2414,10 +2429,10 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -2428,10 +2443,10 @@
         <v>10</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -2442,10 +2457,10 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D120" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -2453,13 +2468,13 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D121" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -2467,13 +2482,13 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -2481,13 +2496,13 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D123" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -2495,13 +2510,13 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -2509,13 +2524,13 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -2526,10 +2541,10 @@
         <v>11</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -2540,10 +2555,10 @@
         <v>11</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -2554,10 +2569,10 @@
         <v>11</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D128" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -2568,10 +2583,10 @@
         <v>11</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D129" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -2582,10 +2597,10 @@
         <v>11</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -2593,13 +2608,13 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -2607,13 +2622,13 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D132" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -2621,13 +2636,13 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C133">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D133" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
@@ -2635,13 +2650,13 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -2649,13 +2664,13 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D135" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -2663,13 +2678,13 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -2680,10 +2695,10 @@
         <v>12</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -2694,10 +2709,10 @@
         <v>12</v>
       </c>
       <c r="C138">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -2708,10 +2723,10 @@
         <v>12</v>
       </c>
       <c r="C139">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D139" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -2722,108 +2737,108 @@
         <v>12</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D140" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D141" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C144">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D144" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D146" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
@@ -2834,10 +2849,10 @@
         <v>9</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
@@ -2845,13 +2860,13 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D149" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
@@ -2859,13 +2874,13 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
@@ -2873,13 +2888,13 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C151">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D151" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
@@ -2887,13 +2902,13 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D152" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
@@ -2901,13 +2916,13 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
@@ -2915,13 +2930,13 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C154">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D154" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
@@ -2929,13 +2944,13 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C155">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
@@ -2946,10 +2961,10 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
@@ -2957,13 +2972,13 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
@@ -2971,13 +2986,13 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D158" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
@@ -2985,13 +3000,13 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D159" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
@@ -2999,13 +3014,13 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D160" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
@@ -3013,13 +3028,13 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
@@ -3027,13 +3042,13 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C162">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D162" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
@@ -3041,13 +3056,13 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C163">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
@@ -3058,10 +3073,10 @@
         <v>11</v>
       </c>
       <c r="C164">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
@@ -3072,10 +3087,10 @@
         <v>11</v>
       </c>
       <c r="C165">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
@@ -3086,10 +3101,10 @@
         <v>11</v>
       </c>
       <c r="C166">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D166" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
@@ -3097,13 +3112,13 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D167" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
@@ -3111,13 +3126,13 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D168" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
@@ -3125,13 +3140,13 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C169">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
@@ -3139,13 +3154,13 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C170">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D170" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
@@ -3153,13 +3168,13 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C171">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D171" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
@@ -3167,13 +3182,13 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C172">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
@@ -3181,13 +3196,13 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C173">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D173" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
@@ -3198,10 +3213,10 @@
         <v>12</v>
       </c>
       <c r="C174">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
@@ -3212,10 +3227,10 @@
         <v>12</v>
       </c>
       <c r="C175">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
@@ -3226,10 +3241,108 @@
         <v>12</v>
       </c>
       <c r="C176">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D176" t="s">
-        <v>73</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177">
+        <v>4</v>
+      </c>
+      <c r="D177" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>12</v>
+      </c>
+      <c r="C178">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>12</v>
+      </c>
+      <c r="C179">
+        <v>6</v>
+      </c>
+      <c r="D179" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>12</v>
+      </c>
+      <c r="C180">
+        <v>7</v>
+      </c>
+      <c r="D180" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>12</v>
+      </c>
+      <c r="C181">
+        <v>8</v>
+      </c>
+      <c r="D181" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>12</v>
+      </c>
+      <c r="C182">
+        <v>9</v>
+      </c>
+      <c r="D182" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>12</v>
+      </c>
+      <c r="C183">
+        <v>10</v>
+      </c>
+      <c r="D183" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Secuencias_Base_APP_AKC.xlsx
+++ b/Secuencias_Base_APP_AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_FFC65FC08FB1EDE630160BFD3BFC529B5A9C7433" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231622A7-B646-6B41-B919-A1DBF73E6870}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E607755A-0C98-B54E-A466-8A6DF3C2F0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="127">
   <si>
     <t>Aparato</t>
   </si>
